--- a/四均線起漲圖表_20260615/四均線起漲精選_20260615.xlsx
+++ b/四均線起漲圖表_20260615/四均線起漲精選_20260615.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,21 +118,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -557,66 +542,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>6691.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>103</v>
+        <v>689</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>21329</v>
+        <v>2580</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>8109</v>
+        <v>1064</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>3413.TW</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>京鼎</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>322</v>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>3.94%</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>4562</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>2263</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -625,7 +576,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
